--- a/docs/data/jp/xlsx/4956.xlsx
+++ b/docs/data/jp/xlsx/4956.xlsx
@@ -1156,7 +1156,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>채권</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -1438,7 +1438,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>화학제품</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -1720,7 +1720,7 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>공사사업</t>
         </is>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -2260,7 +2260,7 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>공사사업</t>
         </is>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -7280,7 +7280,7 @@
     <row r="97">
       <c r="A97" s="18" t="inlineStr">
         <is>
-          <t>Real Estate Rent NOI</t>
+          <t>부동산 임대수입</t>
         </is>
       </c>
       <c r="F97" s="20" t="n">
@@ -7599,7 +7599,7 @@
     <row r="104">
       <c r="A104" s="18" t="inlineStr">
         <is>
-          <t>Rent Cost Of Real Estate NOE</t>
+          <t>부동산 임대원가</t>
         </is>
       </c>
       <c r="F104" s="20" t="n">
@@ -9646,7 +9646,7 @@
     <row r="144">
       <c r="A144" s="18" t="inlineStr">
         <is>
-          <t>부문 · Revenues From External Customers</t>
+          <t>채권 · (1) 외부 고객 매출</t>
         </is>
       </c>
       <c r="C144" s="20" t="n">
@@ -9698,7 +9698,7 @@
     <row r="145">
       <c r="A145" s="18" t="inlineStr">
         <is>
-          <t>부문 · Revenues From External Customers</t>
+          <t>화학제품 · (1) 외부 고객 매출</t>
         </is>
       </c>
       <c r="C145" s="20" t="n">
@@ -9750,7 +9750,7 @@
     <row r="146">
       <c r="A146" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>공사사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="D146" s="20" t="n">
@@ -9852,7 +9852,7 @@
     <row r="149">
       <c r="A149" s="18" t="inlineStr">
         <is>
-          <t>부문 · Revenues From External Customers</t>
+          <t>공사사업 · (1) 외부 고객 매출</t>
         </is>
       </c>
       <c r="F149" s="20" t="n">
@@ -9868,7 +9868,7 @@
     <row r="150">
       <c r="A150" s="18" t="inlineStr">
         <is>
-          <t>합계 · Revenues From External Customers</t>
+          <t>합계 · (1) 외부 고객 매출</t>
         </is>
       </c>
       <c r="C150" s="20" t="n">
@@ -9920,7 +9920,7 @@
     <row r="151">
       <c r="A151" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Revenues From External Customers</t>
+          <t>조정액 · (1) 외부 고객 매출</t>
         </is>
       </c>
       <c r="C151" s="20" t="n">
@@ -9972,7 +9972,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>Revenues From External Customers</t>
+          <t>(1) 외부 고객 매출</t>
         </is>
       </c>
       <c r="C152" s="12" t="n">
@@ -10024,7 +10024,7 @@
     <row r="153">
       <c r="A153" s="18" t="inlineStr">
         <is>
-          <t>부문 · Transactions With Other Segments</t>
+          <t>채권 · (2) 부문 간 내부 매출·대체</t>
         </is>
       </c>
       <c r="C153" s="20" t="n">
@@ -10076,7 +10076,7 @@
     <row r="154">
       <c r="A154" s="18" t="inlineStr">
         <is>
-          <t>부문 · Transactions With Other Segments</t>
+          <t>화학제품 · (2) 부문 간 내부 매출·대체</t>
         </is>
       </c>
       <c r="C154" s="20" t="n">
@@ -10128,7 +10128,7 @@
     <row r="155">
       <c r="A155" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>공사사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="D155" s="20" t="n">
@@ -10230,7 +10230,7 @@
     <row r="158">
       <c r="A158" s="18" t="inlineStr">
         <is>
-          <t>부문 · Transactions With Other Segments</t>
+          <t>공사사업 · (2) 부문 간 내부 매출·대체</t>
         </is>
       </c>
       <c r="F158" s="20" t="n">
@@ -10246,7 +10246,7 @@
     <row r="159">
       <c r="A159" s="18" t="inlineStr">
         <is>
-          <t>합계 · Transactions With Other Segments</t>
+          <t>합계 · (2) 부문 간 내부 매출·대체</t>
         </is>
       </c>
       <c r="C159" s="20" t="n">
@@ -10298,7 +10298,7 @@
     <row r="160">
       <c r="A160" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Transactions With Other Segments</t>
+          <t>조정액 · (2) 부문 간 내부 매출·대체</t>
         </is>
       </c>
       <c r="C160" s="20" t="n">
@@ -10350,7 +10350,7 @@
     <row r="161">
       <c r="A161" s="18" t="inlineStr">
         <is>
-          <t>Transactions With Other Segments</t>
+          <t>(2) 부문 간 내부 매출·대체</t>
         </is>
       </c>
       <c r="C161" s="20" t="n">
@@ -10402,7 +10402,7 @@
     <row r="162">
       <c r="A162" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>채권 · 계</t>
         </is>
       </c>
       <c r="C162" s="20" t="n">
@@ -10454,7 +10454,7 @@
     <row r="163">
       <c r="A163" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>화학제품 · 계</t>
         </is>
       </c>
       <c r="C163" s="20" t="n">
@@ -10506,7 +10506,7 @@
     <row r="164">
       <c r="A164" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>공사사업 · 계</t>
         </is>
       </c>
       <c r="D164" s="20" t="n">
@@ -10608,7 +10608,7 @@
     <row r="167">
       <c r="A167" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>공사사업 · 계</t>
         </is>
       </c>
       <c r="F167" s="20" t="n">
@@ -10780,7 +10780,7 @@
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>채권 · 부문 이익</t>
         </is>
       </c>
       <c r="C171" s="20" t="n">
@@ -10832,7 +10832,7 @@
     <row r="172">
       <c r="A172" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>화학제품 · 부문 이익</t>
         </is>
       </c>
       <c r="C172" s="20" t="n">
@@ -10884,7 +10884,7 @@
     <row r="173">
       <c r="A173" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>공사사업 · 부문 이익</t>
         </is>
       </c>
       <c r="D173" s="20" t="n">
@@ -10986,7 +10986,7 @@
     <row r="176">
       <c r="A176" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>공사사업 · 부문 이익</t>
         </is>
       </c>
       <c r="F176" s="20" t="n">
@@ -11596,7 +11596,7 @@
     <row r="189">
       <c r="A189" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain On Disposal Of Property Plant And Equipment Ope CF</t>
+          <t>유형자산 처분손익</t>
         </is>
       </c>
       <c r="C189" s="20" t="n">
@@ -12666,7 +12666,7 @@
     <row r="212">
       <c r="A212" s="18" t="inlineStr">
         <is>
-          <t>Settlement Package Received Ope CF</t>
+          <t>화해금 수취액</t>
         </is>
       </c>
       <c r="E212" s="20" t="n">
@@ -18528,7 +18528,7 @@
     <row r="122">
       <c r="A122" s="18" t="inlineStr">
         <is>
-          <t>Long Term Guarantee Deposited</t>
+          <t>장기 예수보증금</t>
         </is>
       </c>
       <c r="F122" s="20" t="n">
